--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -23916,12 +23916,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23955,81 +23955,100 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O134" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="R134" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.4205196192727506</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24056,17 +24075,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -24091,7 +24110,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -24100,81 +24119,175 @@
         </is>
       </c>
       <c r="N135" t="n">
+        <v>45</v>
+      </c>
+      <c r="O135" t="n">
+        <v>45</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
         <v>1</v>
       </c>
-      <c r="O135" t="n">
-        <v>1</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24236,7 +24349,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -24245,13 +24358,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O136" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R136" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -24381,7 +24494,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -24526,7 +24639,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24535,13 +24648,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O138" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R138" t="n">
-        <v>0.0489921520703565</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24671,7 +24784,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24680,13 +24793,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24816,7 +24929,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24825,13 +24938,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O140" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R140" t="n">
-        <v>0.04927865588363343</v>
+        <v>0.0489921520703565</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24961,7 +25074,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24970,13 +25083,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -25106,7 +25219,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25115,13 +25228,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="O142" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="R142" t="n">
-        <v>0.05730076265538771</v>
+        <v>0.04927865588363343</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25221,12 +25334,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -25251,109 +25364,90 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25380,17 +25474,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25415,184 +25509,90 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="O144" t="n">
-        <v>2</v>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
+        <v>200</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.05730076265538771</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25624,12 +25624,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25663,13 +25663,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R145" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -25708,7 +25708,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -25716,47 +25716,47 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25788,12 +25788,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25827,24 +25827,24 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -25909,17 +25909,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
@@ -25947,7 +25947,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -25955,45 +25955,448 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV146" t="inlineStr">
+      <c r="AV147" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW146" t="inlineStr">
+      <c r="AW147" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX146" t="inlineStr">
+      <c r="AX147" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY146" t="inlineStr">
+      <c r="AY147" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ146" t="inlineStr">
+      <c r="AZ147" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA146" t="inlineStr">
+      <c r="BA147" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB146" t="inlineStr">
+      <c r="BB147" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC146" t="inlineStr">
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>1</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -26115,7 +26518,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -26125,7 +26528,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -26145,7 +26548,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -26177,7 +26580,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6612</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -25624,12 +25624,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25654,109 +25654,90 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R145" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA145" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25764,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -25827,103 +25808,28 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O146" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD146" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE146" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG146" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN146" t="b">
-        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
@@ -26022,17 +25928,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -26066,29 +25972,104 @@
         </is>
       </c>
       <c r="N147" t="n">
+        <v>6</v>
+      </c>
+      <c r="O147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
         <v>1</v>
       </c>
-      <c r="O147" t="n">
-        <v>1</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26101,7 +26082,7 @@
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -26111,7 +26092,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -26119,47 +26100,47 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26186,7 +26167,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -26235,98 +26216,23 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
+      <c r="R148" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U148" t="inlineStr">
         <is>
           <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -26397,6 +26303,245 @@
         </is>
       </c>
       <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>1</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -26518,7 +26663,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -26528,7 +26673,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -26580,7 +26725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6659</v>
+        <v>6662</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -23552,13 +23552,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O132" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R132" t="n">
-        <v>0.7606596050920676</v>
+        <v>0.7783493633500227</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O133" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -25808,13 +25808,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25972,10 +25972,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R148" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -26375,10 +26375,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6662</v>
+        <v>6672</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -25808,13 +25808,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O146" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25972,10 +25972,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O147" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -26544,6 +26544,151 @@
       <c r="BC149" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>162</v>
+      </c>
+      <c r="O150" t="n">
+        <v>162</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.04641361775086404</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26725,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26808,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -26673,7 +26818,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -26725,7 +26870,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6672</v>
+        <v>6836</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O39" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O40" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O57" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -10601,10 +10601,10 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O58" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -13621,10 +13621,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O75" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13777,10 +13777,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O76" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -17090,10 +17090,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O95" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17246,10 +17246,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O96" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -20203,12 +20203,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20242,22 +20242,19 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="O113" t="n">
-        <v>22</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0.3913380175901103</v>
+        <v>109</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -20272,70 +20269,65 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20367,12 +20359,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20406,24 +20398,24 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="O114" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
@@ -20438,7 +20430,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -20453,7 +20445,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -20488,17 +20480,17 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+          <t>PHO IDTO current-year monthly preliminary giardiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -20511,70 +20503,65 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20606,12 +20593,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20645,13 +20632,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O115" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="R115" t="n">
-        <v>0.5130029894806968</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20660,7 +20647,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -20680,7 +20667,7 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
@@ -20690,7 +20677,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -20698,47 +20685,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20770,12 +20757,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20809,24 +20796,24 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="O116" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -20856,7 +20843,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -20891,17 +20878,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20919,7 +20906,7 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
@@ -20929,7 +20916,7 @@
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20937,47 +20924,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21009,12 +20996,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -21048,13 +21035,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="O117" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="R117" t="n">
-        <v>1.078018465888942</v>
+        <v>0.5130029894806968</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -21063,7 +21050,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -21078,7 +21065,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -21086,57 +21073,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21168,12 +21160,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -21207,24 +21199,24 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="O118" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
@@ -21239,7 +21231,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -21254,7 +21246,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -21289,17 +21281,17 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -21312,7 +21304,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -21320,57 +21312,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21402,12 +21399,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21441,13 +21438,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="O119" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="R119" t="n">
-        <v>0.214932249850517</v>
+        <v>1.078018465888942</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -21456,7 +21453,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -21471,7 +21468,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -21479,62 +21476,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21566,12 +21558,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21605,29 +21597,29 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="O120" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -21637,7 +21629,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -21652,7 +21644,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -21687,17 +21679,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -21710,7 +21702,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21718,62 +21710,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21805,12 +21792,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21835,7 +21822,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -21844,81 +21831,100 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.214932249850517</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21945,17 +21951,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21980,7 +21986,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21989,81 +21995,175 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="O122" t="n">
-        <v>104</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0.0297963965808016</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22125,7 +22225,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -22134,13 +22234,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -22270,7 +22370,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22279,13 +22379,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="O124" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="R124" t="n">
-        <v>0.03982403004549445</v>
+        <v>0.0297963965808016</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -22415,7 +22515,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22560,7 +22660,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22569,13 +22669,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O126" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="R126" t="n">
-        <v>0.04784613681724874</v>
+        <v>0.03982403004549445</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -22705,7 +22805,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22714,13 +22814,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22850,7 +22950,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22859,13 +22959,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="O128" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="R128" t="n">
-        <v>0.05987929697488016</v>
+        <v>0.04784613681724874</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22995,7 +23095,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -23110,12 +23210,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -23140,109 +23240,90 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="O130" t="n">
-        <v>14</v>
+        <v>209</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2490332839209793</v>
+        <v>0.05987929697488016</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23269,17 +23350,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -23304,184 +23385,90 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>14</v>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23513,12 +23500,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23552,13 +23539,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O132" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="R132" t="n">
-        <v>0.7783493633500227</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23567,7 +23554,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -23587,7 +23574,7 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -23597,7 +23584,7 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -23605,47 +23592,47 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23677,12 +23664,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23716,24 +23703,24 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O133" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -23763,7 +23750,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -23798,17 +23785,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -23826,7 +23813,7 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
@@ -23836,7 +23823,7 @@
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -23844,47 +23831,47 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23916,12 +23903,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23955,13 +23942,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O134" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R134" t="n">
-        <v>0.4205196192727506</v>
+        <v>0.7783493633500227</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23970,7 +23957,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -24000,7 +23987,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -24013,42 +24000,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24080,12 +24067,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -24119,29 +24106,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O135" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -24166,7 +24153,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -24201,17 +24188,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -24239,7 +24226,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -24252,42 +24239,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24319,12 +24306,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -24358,81 +24345,100 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O136" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="R136" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.4205196192727506</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24459,17 +24465,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24494,7 +24500,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -24503,81 +24509,175 @@
         </is>
       </c>
       <c r="N137" t="n">
+        <v>45</v>
+      </c>
+      <c r="O137" t="n">
+        <v>45</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
         <v>1</v>
       </c>
-      <c r="O137" t="n">
-        <v>1</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24639,7 +24739,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24648,13 +24748,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O138" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R138" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24784,7 +24884,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24929,7 +25029,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24938,13 +25038,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O140" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0489921520703565</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -25074,7 +25174,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -25083,13 +25183,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -25219,7 +25319,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25228,13 +25328,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O142" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R142" t="n">
-        <v>0.04927865588363343</v>
+        <v>0.0489921520703565</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25364,7 +25464,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -25373,13 +25473,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25509,7 +25609,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25518,13 +25618,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="O144" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="R144" t="n">
-        <v>0.05730076265538771</v>
+        <v>0.04927865588363343</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -25654,7 +25754,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25769,12 +25869,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25799,109 +25899,90 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N146" t="n">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="O146" t="n">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.05730076265538771</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA146" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25928,17 +26009,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25963,184 +26044,90 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N147" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>9</v>
-      </c>
-      <c r="U147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y147" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD147" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE147" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN147" t="b">
         <v>1</v>
       </c>
+      <c r="R147" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26172,12 +26159,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -26217,7 +26204,7 @@
         <v>9</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1600928253777724</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -26226,7 +26213,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -26246,7 +26233,7 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
@@ -26256,7 +26243,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -26264,47 +26251,47 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26336,12 +26323,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26382,17 +26369,17 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
@@ -26422,7 +26409,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -26457,17 +26444,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -26485,7 +26472,7 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
@@ -26495,7 +26482,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -26503,47 +26490,47 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26575,118 +26562,521 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>9</v>
+      </c>
+      <c r="O150" t="n">
+        <v>9</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.1592078243215956</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>9</v>
+      </c>
+      <c r="O151" t="n">
+        <v>9</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM151" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN151" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>D099</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>贾第虫病</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="K152" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N150" t="n">
+      <c r="N152" t="n">
         <v>162</v>
       </c>
-      <c r="O150" t="n">
+      <c r="O152" t="n">
         <v>162</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R152" t="n">
         <v>0.04641361775086404</v>
       </c>
-      <c r="S150" t="inlineStr">
+      <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO150" t="inlineStr">
+      <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP150" t="inlineStr">
+      <c r="AP152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR150" t="inlineStr">
+      <c r="AR152" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS150" t="inlineStr"/>
-      <c r="AT150" t="n">
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
         <v>0</v>
       </c>
-      <c r="AU150" t="inlineStr">
+      <c r="AU152" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV150" t="inlineStr">
+      <c r="AV152" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW150" t="inlineStr">
+      <c r="AW152" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX150" t="inlineStr">
+      <c r="AX152" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY150" t="inlineStr">
+      <c r="AY152" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ150" t="inlineStr">
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA150" t="inlineStr">
+      <c r="BA152" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB150" t="inlineStr">
+      <c r="BB152" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC150" t="inlineStr">
+      <c r="BC152" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -26808,7 +27198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -26818,7 +27208,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -26838,7 +27228,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -26870,7 +27260,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6836</v>
+        <v>6959</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -26198,13 +26198,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -26362,10 +26362,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6959</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -27082,6 +27082,151 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
+        <v>1</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27115,7 +27260,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -27198,7 +27343,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -27208,7 +27353,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -27260,7 +27405,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6960</v>
+        <v>6961</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -24306,12 +24306,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -24345,13 +24345,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O136" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="R136" t="n">
-        <v>0.4205196192727506</v>
+        <v>1.021280651894788</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -24375,7 +24375,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -24383,62 +24383,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24470,12 +24465,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24509,29 +24504,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O137" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -24541,7 +24536,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -24556,7 +24551,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -24591,17 +24586,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -24614,7 +24609,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24622,62 +24617,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24709,12 +24699,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24748,81 +24738,100 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O138" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="R138" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.4205196192727506</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24849,17 +24858,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24884,7 +24893,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24893,81 +24902,175 @@
         </is>
       </c>
       <c r="N139" t="n">
+        <v>45</v>
+      </c>
+      <c r="O139" t="n">
+        <v>45</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
         <v>1</v>
       </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25132,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -25038,13 +25141,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O140" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R140" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -25174,7 +25277,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -25319,7 +25422,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25328,13 +25431,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O142" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0489921520703565</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25464,7 +25567,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -25473,13 +25576,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -25609,7 +25712,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25618,13 +25721,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O144" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R144" t="n">
-        <v>0.04927865588363343</v>
+        <v>0.0489921520703565</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -25754,7 +25857,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25763,13 +25866,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25899,7 +26002,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25908,13 +26011,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="O146" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="R146" t="n">
-        <v>0.05730076265538771</v>
+        <v>0.04927865588363343</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -26044,7 +26147,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -26159,12 +26262,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -26189,109 +26292,90 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N148" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="O148" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.05730076265538771</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26318,17 +26402,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26353,184 +26437,90 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>10</v>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
         <v>1</v>
       </c>
+      <c r="R149" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26562,12 +26552,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26601,13 +26591,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26616,7 +26606,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -26636,7 +26626,7 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
@@ -26646,7 +26636,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -26654,47 +26644,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26726,12 +26716,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26765,24 +26755,24 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
@@ -26812,7 +26802,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -26847,17 +26837,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -26875,7 +26865,7 @@
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
@@ -26885,7 +26875,7 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -26893,47 +26883,47 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26965,12 +26955,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26995,7 +26985,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -27004,81 +26994,100 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="O152" t="n">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="R152" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27105,123 +27114,507 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>9</v>
+      </c>
+      <c r="O153" t="n">
+        <v>9</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>162</v>
+      </c>
+      <c r="O154" t="n">
+        <v>162</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.04641361775086404</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>D099</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
         <is>
           <t>贾第虫病</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="K155" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N153" t="n">
+      <c r="N155" t="n">
         <v>1</v>
       </c>
-      <c r="O153" t="n">
+      <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="R153" t="n">
+      <c r="R155" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S153" t="inlineStr">
+      <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO153" t="inlineStr">
+      <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP153" t="inlineStr">
+      <c r="AP155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR153" t="inlineStr">
+      <c r="AR155" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS153" t="inlineStr"/>
-      <c r="AT153" t="n">
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
         <v>0</v>
       </c>
-      <c r="AU153" t="inlineStr">
+      <c r="AU155" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV153" t="inlineStr">
+      <c r="AV155" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW153" t="inlineStr">
+      <c r="AW155" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX153" t="inlineStr">
+      <c r="AX155" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY153" t="inlineStr">
+      <c r="AY155" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ153" t="inlineStr">
+      <c r="AZ155" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA153" t="inlineStr">
+      <c r="BA155" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB153" t="inlineStr">
+      <c r="BB155" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC153" t="inlineStr">
+      <c r="BC155" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27343,7 +27736,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -27353,7 +27746,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -27373,7 +27766,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -27405,7 +27798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6961</v>
+        <v>7015</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -26994,13 +26994,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O152" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27158,10 +27158,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O153" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7015</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -26591,13 +26591,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O150" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O151" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -27798,7 +27798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7020</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -27620,6 +27620,151 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>288</v>
+      </c>
+      <c r="O156" t="n">
+        <v>288</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.0825130982237583</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27653,7 +27798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -27736,7 +27881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -27746,7 +27891,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -27798,7 +27943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7021</v>
+        <v>7309</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -23942,13 +23942,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O134" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R134" t="n">
-        <v>0.7783493633500227</v>
+        <v>0.7960391216079779</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -24106,10 +24106,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O135" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -26591,13 +26591,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O150" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O151" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -26994,13 +26994,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O152" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="R152" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.4599337147068316</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27158,10 +27158,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="O153" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -27760,6 +27760,296 @@
         </is>
       </c>
       <c r="BC156" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>185</v>
+      </c>
+      <c r="O158" t="n">
+        <v>185</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.05300320545623363</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -27798,7 +28088,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -27881,7 +28171,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -27891,7 +28181,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -27943,7 +28233,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7309</v>
+        <v>7514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -26591,13 +26591,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O150" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R150" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26755,10 +26755,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O151" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -28052,6 +28052,699 @@
       <c r="BC158" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>195</v>
+      </c>
+      <c r="O160" t="n">
+        <v>195</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.05586824358900301</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28088,7 +28781,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -28171,7 +28864,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -28181,7 +28874,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -28201,7 +28894,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -28233,7 +28926,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7514</v>
+        <v>7718</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -26994,13 +26994,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O152" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R152" t="n">
-        <v>0.4599337147068316</v>
+        <v>0.5306927477386518</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27158,10 +27158,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="O153" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -28926,7 +28926,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7718</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -28373,12 +28373,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -28403,109 +28403,90 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N161" t="n">
+        <v>1</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
         <v>0</v>
       </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AT161" t="n">
-        <v>2</v>
-      </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28532,7 +28513,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -28581,98 +28562,23 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
@@ -28743,6 +28649,245 @@
         </is>
       </c>
       <c r="BC162" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -28864,7 +29009,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -28874,7 +29019,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -28926,7 +29071,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7722</v>
+        <v>7723</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2771,6 +2771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3067,6 +3072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3363,6 +3373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3659,6 +3674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3955,6 +3975,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4087,10 +4112,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -4243,10 +4268,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O22" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5136,7 +5161,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6246,6 +6271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6542,6 +6572,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6838,6 +6873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7134,6 +7174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8315,7 +8360,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9425,6 +9470,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9721,6 +9771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10017,6 +10072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10313,6 +10373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10445,10 +10510,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O57" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -10601,10 +10666,10 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O58" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -11494,7 +11559,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12601,6 +12666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12897,6 +12967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13193,6 +13268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13489,6 +13569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13621,10 +13706,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O75" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -13777,10 +13862,10 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O76" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U76" t="inlineStr">
         <is>
@@ -14670,7 +14755,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15777,6 +15862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16073,6 +16163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16369,6 +16464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16665,6 +16765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16958,6 +17063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17090,10 +17200,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O95" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17246,10 +17356,10 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O96" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U96" t="inlineStr">
         <is>
@@ -18139,7 +18249,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -19240,6 +19350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19530,6 +19645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19820,6 +19940,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20110,6 +20235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20242,10 +20372,10 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="O113" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -20398,10 +20528,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="O114" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -21291,7 +21421,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -22392,6 +22522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22682,6 +22817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22972,6 +23112,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23262,6 +23407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23500,12 +23650,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23539,22 +23689,19 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="O132" t="n">
-        <v>14</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0.2490332839209793</v>
+        <v>118</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -23569,70 +23716,65 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23664,12 +23806,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23703,24 +23845,24 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="O133" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
@@ -23735,7 +23877,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -23750,7 +23892,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -23785,17 +23927,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+          <t>PHO IDTO current-year monthly preliminary giardiasis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -23808,70 +23950,65 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1280</t>
+          <t>SER_CA_ON_PHO_IDTO_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23903,12 +24040,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23942,13 +24079,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="O134" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="R134" t="n">
-        <v>0.7960391216079779</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23957,7 +24094,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -23977,7 +24114,7 @@
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
@@ -23987,7 +24124,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -23995,47 +24132,47 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24067,12 +24204,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -24106,24 +24243,24 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="O135" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
@@ -24153,7 +24290,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -24188,17 +24325,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -24216,7 +24353,7 @@
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -24226,7 +24363,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -24234,47 +24371,47 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24306,12 +24443,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -24345,13 +24482,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="O136" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="R136" t="n">
-        <v>1.021280651894788</v>
+        <v>0.7960391216079779</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -24360,7 +24497,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -24375,7 +24512,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -24383,57 +24520,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24465,12 +24607,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24504,24 +24646,24 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="O137" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -24536,7 +24678,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -24551,7 +24693,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -24586,17 +24728,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -24609,7 +24751,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
@@ -24617,57 +24759,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
+          <t>SER_NO_FHI_305_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24699,12 +24846,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24738,13 +24885,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O138" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="R138" t="n">
-        <v>0.4205196192727506</v>
+        <v>1.021280651894788</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24753,7 +24900,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -24768,7 +24915,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24776,62 +24923,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24863,12 +25005,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24902,29 +25044,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O139" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Giardiainfektion</t>
+          <t>Giardiasis</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -24934,7 +25076,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -24949,7 +25091,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -24984,17 +25126,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly giardiasis notifications.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -25007,7 +25149,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -25015,62 +25157,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+          <t>SER_NZ_GIARDIASIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25102,12 +25239,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25141,81 +25278,100 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="O140" t="n">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="R140" t="n">
-        <v>0.05243019782967975</v>
+        <v>0.4205196192727506</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25242,17 +25398,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -25277,7 +25433,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -25286,81 +25442,175 @@
         </is>
       </c>
       <c r="N141" t="n">
+        <v>45</v>
+      </c>
+      <c r="O141" t="n">
+        <v>45</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25422,7 +25672,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -25431,17 +25681,22 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="O142" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="R142" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.05243019782967975</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -25567,7 +25822,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -25712,7 +25967,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25721,17 +25976,22 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O144" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R144" t="n">
-        <v>0.0489921520703565</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -25857,7 +26117,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25866,13 +26126,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -26002,7 +26262,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -26011,17 +26271,22 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O146" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="R146" t="n">
-        <v>0.04927865588363343</v>
+        <v>0.0489921520703565</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -26147,7 +26412,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -26156,13 +26421,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -26292,7 +26557,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -26301,17 +26566,22 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="O148" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="R148" t="n">
-        <v>0.05730076265538771</v>
+        <v>0.04927865588363343</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -26437,7 +26707,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -26552,12 +26822,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26582,109 +26852,95 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="O150" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="R150" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.05730076265538771</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26711,17 +26967,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26746,184 +27002,90 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>25</v>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
         <v>1</v>
       </c>
+      <c r="R151" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26955,12 +27117,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26994,13 +27156,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O152" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R152" t="n">
-        <v>0.5306927477386518</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27009,7 +27171,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -27029,7 +27191,7 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
@@ -27039,7 +27201,7 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -27047,47 +27209,47 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27119,12 +27281,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27158,24 +27320,24 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O153" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
@@ -27205,7 +27367,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -27240,17 +27402,17 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -27268,7 +27430,7 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
@@ -27278,7 +27440,7 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_305_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1280</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -27286,47 +27448,47 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27358,12 +27520,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -27388,7 +27550,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -27397,81 +27559,100 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="O154" t="n">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="R154" t="n">
-        <v>0.04641361775086404</v>
+        <v>0.583762022512517</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27498,17 +27679,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27533,7 +27714,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -27542,81 +27723,175 @@
         </is>
       </c>
       <c r="N155" t="n">
+        <v>33</v>
+      </c>
+      <c r="O155" t="n">
+        <v>33</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
         <v>1</v>
       </c>
-      <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27648,12 +27923,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27678,7 +27953,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -27687,81 +27962,100 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>288</v>
+        <v>44</v>
       </c>
       <c r="O156" t="n">
-        <v>288</v>
+        <v>44</v>
       </c>
       <c r="R156" t="n">
-        <v>0.0825130982237583</v>
+        <v>0.4111747388444672</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27788,17 +28082,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27823,7 +28117,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -27832,81 +28126,175 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Giardiainfektion</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_GIARDIA</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27968,7 +28356,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -27977,17 +28365,22 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="O158" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="R158" t="n">
-        <v>0.05300320545623363</v>
+        <v>0.04641361775086404</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -28113,7 +28506,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -28122,13 +28515,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -28258,7 +28651,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -28267,17 +28660,22 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="O160" t="n">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="R160" t="n">
-        <v>0.05586824358900301</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -28403,7 +28801,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -28412,13 +28810,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -28518,12 +28916,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28548,109 +28946,95 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N162" t="n">
+        <v>185</v>
+      </c>
+      <c r="O162" t="n">
+        <v>185</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.05300320545623363</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
         <v>0</v>
       </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AT162" t="n">
-        <v>2</v>
-      </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28677,219 +29061,1376 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>195</v>
+      </c>
+      <c r="O164" t="n">
+        <v>195</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.05586824358900301</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>7</v>
+      </c>
+      <c r="O166" t="n">
+        <v>7</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>D099</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>贾第虫病</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N163" t="n">
+      <c r="N167" t="n">
+        <v>7</v>
+      </c>
+      <c r="O167" t="n">
+        <v>7</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1280</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>7</v>
+      </c>
+      <c r="O168" t="n">
+        <v>7</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.1238283078056854</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>7</v>
+      </c>
+      <c r="O169" t="n">
+        <v>7</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_305_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>187</v>
+      </c>
+      <c r="O170" t="n">
+        <v>187</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.0535762130827875</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
         <v>0</v>
       </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="V163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="W163" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X163" t="inlineStr">
-        <is>
-          <t>Giardiasis</t>
-        </is>
-      </c>
-      <c r="Y163" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD163" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE163" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG163" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH163" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1280.</t>
-        </is>
-      </c>
-      <c r="AM163" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN163" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1280</t>
-        </is>
-      </c>
-      <c r="AT163" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV163" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
-      <c r="AW163" t="inlineStr">
-        <is>
-          <t>Finland THL Infectious Diseases Register</t>
-        </is>
-      </c>
-      <c r="AX163" t="inlineStr">
-        <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t>cube_csv</t>
-        </is>
-      </c>
-      <c r="AZ163" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
-      <c r="BA163" t="inlineStr">
-        <is>
-          <t>Finland THL Infectious Diseases Register</t>
-        </is>
-      </c>
-      <c r="BB163" t="inlineStr">
-        <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
-        </is>
-      </c>
-      <c r="BC163" t="inlineStr">
-        <is>
-          <t>cube_csv</t>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28926,7 +30467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -29009,7 +30550,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -29019,7 +30560,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -29039,7 +30580,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -29071,7 +30612,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7723</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -27156,13 +27156,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O152" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R152" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.4624903844246757</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27320,10 +27320,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O153" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -29545,13 +29545,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O166" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R166" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -29709,10 +29709,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O167" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
@@ -30612,7 +30612,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8107</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -29948,13 +29948,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O168" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30112,10 +30112,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O169" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -30431,6 +30431,151 @@
       <c r="BC170" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" t="n">
+        <v>4</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30467,7 +30612,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -30550,7 +30695,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -30560,7 +30705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -30612,7 +30757,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8109</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d099/2026-2029.xlsx
+++ b/diseases/d099/2026-2029.xlsx
@@ -2760,9 +2760,6 @@
       <c r="O12" t="n">
         <v>42</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -3061,9 +3058,6 @@
       <c r="O14" t="n">
         <v>124</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.03552647284634038</v>
       </c>
@@ -3362,9 +3356,6 @@
       <c r="O16" t="n">
         <v>111</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.03180192327374018</v>
       </c>
@@ -3663,9 +3654,6 @@
       <c r="O18" t="n">
         <v>115</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.03294793852684793</v>
       </c>
@@ -3964,9 +3952,6 @@
       <c r="O20" t="n">
         <v>96</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.0275043660745861</v>
       </c>
@@ -6255,16 +6240,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O32" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="R32" t="n">
-        <v>0.03380744996667875</v>
+        <v>0.03352094615340181</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6556,16 +6538,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O34" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="R34" t="n">
-        <v>0.03667248809944813</v>
+        <v>0.03609948047289425</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -6857,16 +6836,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O36" t="n">
-        <v>125</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="R36" t="n">
-        <v>0.03581297665961732</v>
+        <v>0.03523996903306344</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7158,16 +7134,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O38" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="R38" t="n">
-        <v>0.04211606055170997</v>
+        <v>0.04154305292515609</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -9459,9 +9432,6 @@
       <c r="O50" t="n">
         <v>122</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0349534652197865</v>
       </c>
@@ -9755,16 +9725,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O52" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04154305292515609</v>
+        <v>0.04097004529860222</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10056,16 +10023,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="O54" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="R54" t="n">
-        <v>0.03380744996667875</v>
+        <v>0.032661434713571</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10357,16 +10321,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O56" t="n">
-        <v>130</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="R56" t="n">
-        <v>0.03724549572600201</v>
+        <v>0.03695899191272507</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -12650,16 +12611,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O68" t="n">
-        <v>170</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="R68" t="n">
-        <v>0.04870564825707954</v>
+        <v>0.04841914444380261</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -12956,9 +12914,6 @@
       <c r="O70" t="n">
         <v>158</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.04526760249775628</v>
       </c>
@@ -13252,16 +13207,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O72" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="R72" t="n">
-        <v>0.04526760249775628</v>
+        <v>0.04469459487120241</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -13553,16 +13505,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O74" t="n">
-        <v>170</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="R74" t="n">
-        <v>0.04870564825707954</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -15851,9 +15800,6 @@
       <c r="O86" t="n">
         <v>159</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.04555410631103323</v>
       </c>
@@ -16152,9 +16098,6 @@
       <c r="O88" t="n">
         <v>161</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.0461271139375871</v>
       </c>
@@ -16453,9 +16396,6 @@
       <c r="O90" t="n">
         <v>141</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.04039703767204833</v>
       </c>
@@ -16754,9 +16694,6 @@
       <c r="O92" t="n">
         <v>94</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.02693135844803222</v>
       </c>
@@ -30576,6 +30513,156 @@
       <c r="BC171" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>giardiasis</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Giardiasis</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>贾第虫病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>147</v>
+      </c>
+      <c r="O172" t="n">
+        <v>147</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.04211606055170997</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30612,7 +30699,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -30695,7 +30782,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -30705,7 +30792,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -30757,7 +30844,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8120</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="16">
